--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484642_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484642_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4372</v>
+        <v>5.2609</v>
       </c>
       <c r="E2" t="n">
-        <v>2.439</v>
+        <v>2.5352</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9982</v>
+        <v>2.7257</v>
       </c>
       <c r="G2" t="n">
         <v>6.6434</v>
@@ -610,13 +610,13 @@
         <v>0.9163</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9563</v>
+        <v>0.78</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0905</v>
+        <v>0.1867</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8658</v>
+        <v>0.5933</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2461</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9363</v>
+        <v>3.7189</v>
       </c>
       <c r="E3" t="n">
-        <v>0.206</v>
+        <v>0.261</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7303</v>
+        <v>3.4578</v>
       </c>
       <c r="G3" t="n">
         <v>2.8397</v>
@@ -688,13 +688,13 @@
         <v>2.0158</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0708</v>
+        <v>-0.2883</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5158</v>
+        <v>-0.4608</v>
       </c>
       <c r="U3" t="n">
-        <v>0.445</v>
+        <v>0.1725</v>
       </c>
       <c r="V3" t="n">
         <v>1.9005</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LORENTE</t>
+          <t>H. RUEDA RIOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2249</v>
+        <v>3.1638</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1712</v>
+        <v>0.0172</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0537</v>
+        <v>3.1466</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7632</v>
+        <v>-1.9772</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0231</v>
+        <v>1.9844</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2599</v>
+        <v>-3.9616</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6048</v>
+        <v>-1.5982</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4798</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.125</v>
+        <v>-2.4868</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1584</v>
+        <v>-0.379</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5433</v>
+        <v>1.0958</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3849</v>
+        <v>-1.4748</v>
       </c>
       <c r="P4" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R4" t="n">
-        <v>0.733</v>
+        <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7495000000000001</v>
+        <v>0.7562</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5664</v>
+        <v>-0.0022</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1832</v>
+        <v>0.7585</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0208</v>
+        <v>3.4686</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0208</v>
+        <v>0.9346</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. RUEDA RIOS</t>
+          <t>J. JIMENEZ LORENTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8653</v>
+        <v>2.9201</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.752</v>
+        <v>1.8416</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6173</v>
+        <v>1.0785</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.9772</v>
+        <v>1.7632</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9844</v>
+        <v>2.0231</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.9616</v>
+        <v>-0.2599</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.5982</v>
+        <v>1.6048</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8885999999999999</v>
+        <v>1.4798</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.4868</v>
+        <v>0.125</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.379</v>
+        <v>0.1584</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0958</v>
+        <v>0.5433</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4748</v>
+        <v>-0.3849</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8326</v>
+        <v>0.733</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4577</v>
+        <v>0.4448</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7715</v>
+        <v>0.2368</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2291</v>
+        <v>0.2079</v>
       </c>
       <c r="V5" t="n">
-        <v>3.4686</v>
+        <v>-0.0208</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.9346</v>
+        <v>-0.0208</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1243</v>
+        <v>1.0838</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5088</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6155</v>
+        <v>1.9623</v>
       </c>
       <c r="G6" t="n">
         <v>-1.8482</v>
@@ -922,13 +922,13 @@
         <v>2.5656</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2448</v>
+        <v>1.2044</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9933</v>
+        <v>0.606</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2516</v>
+        <v>0.5984</v>
       </c>
       <c r="V6" t="n">
         <v>1.9109</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. FAJARDO PAÑOS</t>
+          <t>R. RAMOS SAN SEBASTIAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6251</v>
+        <v>1.0517</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6251</v>
+        <v>-0.4937</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.5454</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6251</v>
+        <v>1.4456</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.0738</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6251</v>
+        <v>1.3718</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6251</v>
+        <v>1.3453</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.155</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6251</v>
+        <v>1.5003</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.1003</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.2288</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.1285</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-1.1269</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.9227</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.2042</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. ROIG VALERO</t>
+          <t>C. FAJARDO PAÑOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,37 +1033,37 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1864</v>
+        <v>0.6251</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0417</v>
+        <v>0.6251</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1447</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1699</v>
+        <v>0.6251</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1282</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0417</v>
+        <v>0.6251</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0417</v>
+        <v>0.6251</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0417</v>
+        <v>0.6251</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1282</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1282</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0165</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0165</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. RAMOS SAN SEBASTIAN</t>
+          <t>O. ROIG VALERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1384</v>
+        <v>0.2112</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8372000000000001</v>
+        <v>0.0417</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9756</v>
+        <v>0.1695</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4456</v>
+        <v>0.1699</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0738</v>
+        <v>0.1282</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3718</v>
+        <v>0.0417</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3453</v>
+        <v>0.0417</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.155</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5003</v>
+        <v>0.0417</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1003</v>
+        <v>0.1282</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2288</v>
+        <v>0.1282</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1285</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0402</v>
+        <v>0.0413</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2662</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.774</v>
+        <v>0.0413</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. PRADA SANCHEZ</t>
+          <t>D. FERNANDEZ NARRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6781</v>
+        <v>-0.3369</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3497</v>
+        <v>-1.284</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6716</v>
+        <v>0.947</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3406</v>
+        <v>-0.227</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5893</v>
+        <v>0.5327</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9298999999999999</v>
+        <v>-0.7597</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9958</v>
+        <v>-0.491</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2259</v>
+        <v>0.1084</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7698</v>
+        <v>-0.5994</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6552</v>
+        <v>0.264</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8152</v>
+        <v>0.4243</v>
       </c>
       <c r="O10" t="n">
-        <v>0.16</v>
+        <v>-0.1603</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3665</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1991</v>
+        <v>0.5498</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7621</v>
+        <v>0.2566</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1568</v>
+        <v>0.1233</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3947</v>
+        <v>0.1333</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ NARRO</t>
+          <t>V. PRADA SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7493</v>
+        <v>-0.3376</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5724</v>
+        <v>-0.9101</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.5725</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.227</v>
+        <v>0.3406</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5327</v>
+        <v>-0.5893</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7597</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.491</v>
+        <v>0.9958</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1084</v>
+        <v>0.2259</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5994</v>
+        <v>0.7698</v>
       </c>
       <c r="M11" t="n">
-        <v>0.264</v>
+        <v>-0.6552</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4243</v>
+        <v>-0.8152</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1603</v>
+        <v>0.16</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3665</v>
+        <v>0.3665</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5498</v>
+        <v>2.1991</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1557</v>
+        <v>-0.4216</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1652</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0094</v>
+        <v>0.2956</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0247</v>
+        <v>-1.2418</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8262</v>
+        <v>-2.0185</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8015</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3302</v>
@@ -1390,13 +1390,13 @@
         <v>1.8326</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2218</v>
+        <v>0.0047</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.2677</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2972</v>
+        <v>0.2724</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.3182</v>
+        <v>-1.2716</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.427</v>
+        <v>-1.3308</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1087</v>
+        <v>0.0592</v>
       </c>
       <c r="G13" t="n">
         <v>0.6673</v>
@@ -1468,13 +1468,13 @@
         <v>0.733</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2525</v>
+        <v>-0.2059</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4404</v>
+        <v>-0.3443</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1879</v>
+        <v>0.1384</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6335</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.5618</v>
+        <v>-1.3666</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.457</v>
+        <v>-2.3609</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8952</v>
+        <v>0.9943</v>
       </c>
       <c r="G14" t="n">
         <v>-0.29</v>
@@ -1546,13 +1546,13 @@
         <v>0.5498</v>
       </c>
       <c r="S14" t="n">
-        <v>0.011</v>
+        <v>0.2063</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1101</v>
+        <v>-0.0139</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1211</v>
+        <v>0.2202</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>13.2058</v>
+        <v>13.481</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.2297</v>
+        <v>-3.954699999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>17.4354</v>
+        <v>17.4355</v>
       </c>
       <c r="G15" t="n">
         <v>9.822200000000002</v>
@@ -1600,10 +1600,10 @@
         <v>7.971399999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>2.199000000000001</v>
+        <v>2.199</v>
       </c>
       <c r="L15" t="n">
-        <v>5.7721</v>
+        <v>5.772099999999999</v>
       </c>
       <c r="M15" t="n">
         <v>1.8507</v>
@@ -1624,13 +1624,13 @@
         <v>15.5769</v>
       </c>
       <c r="S15" t="n">
-        <v>1.376300000000001</v>
+        <v>1.6516</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.8512</v>
+        <v>-1.576</v>
       </c>
       <c r="U15" t="n">
-        <v>3.2275</v>
+        <v>3.2276</v>
       </c>
       <c r="V15" t="n">
         <v>4.7565</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4825</v>
+        <v>2.9112</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6206</v>
+        <v>1.8129</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8619</v>
+        <v>1.0983</v>
       </c>
       <c r="G16" t="n">
         <v>0.212</v>
@@ -1702,13 +1702,13 @@
         <v>2.1991</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8187</v>
+        <v>0.2474</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.5249</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5358</v>
+        <v>0.7722</v>
       </c>
       <c r="V16" t="n">
         <v>2.0853</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. BORISOV</t>
+          <t>E. CHOFRE TARREGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9094</v>
+        <v>1.1037</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.3646</v>
+        <v>1.8845</v>
       </c>
       <c r="F17" t="n">
-        <v>3.274</v>
+        <v>-0.7808</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4575</v>
+        <v>1.3949</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4911</v>
+        <v>-0.6249</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9487</v>
+        <v>2.0198</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3411</v>
+        <v>3.178</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2227</v>
+        <v>0.5169</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5637</v>
+        <v>2.6611</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1164</v>
+        <v>-1.7831</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2685</v>
+        <v>-1.1418</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3849</v>
+        <v>-0.6413</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5498</v>
+        <v>1.6493</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1991</v>
+        <v>1.6493</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6393</v>
+        <v>-0.5364</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.552</v>
+        <v>-0.6704</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1914</v>
+        <v>0.134</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2774</v>
+        <v>-1.4041</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2774</v>
+        <v>-0.6231</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.781</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. CHOFRE TARREGA</t>
+          <t>D. BORISOV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5603</v>
+        <v>0.6645</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6922</v>
+        <v>-2.1722</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1319</v>
+        <v>2.8368</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3949</v>
+        <v>-0.4575</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6249</v>
+        <v>0.4911</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0198</v>
+        <v>-0.9487</v>
       </c>
       <c r="J18" t="n">
-        <v>3.178</v>
+        <v>-0.3411</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5169</v>
+        <v>0.2227</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6611</v>
+        <v>-0.5637</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7831</v>
+        <v>-0.1164</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1418</v>
+        <v>0.2685</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6413</v>
+        <v>-0.3849</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6493</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6493</v>
+        <v>2.1991</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0799</v>
+        <v>0.3944</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8627</v>
+        <v>-0.3597</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2171</v>
+        <v>0.7541</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4041</v>
+        <v>1.2774</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6231</v>
+        <v>1.2774</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.781</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4641</v>
+        <v>-0.8124</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8136</v>
+        <v>-1.2943</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3494</v>
+        <v>0.482</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4238</v>
@@ -1936,13 +1936,13 @@
         <v>1.4661</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9989</v>
+        <v>0.6506</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4193</v>
+        <v>-0.0614</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5795</v>
+        <v>0.7121</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5889</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ROIG MESA</t>
+          <t>E. DENIA VIVANCOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4344</v>
+        <v>-1.0817</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1385</v>
+        <v>-3.245</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.296</v>
+        <v>2.1632</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8533</v>
+        <v>-0.7365</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9977</v>
+        <v>-0.3067</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1444</v>
+        <v>-0.4298</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3663</v>
+        <v>-1.2703</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.152</v>
+        <v>-1.3536</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7857</v>
+        <v>0.0833</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.487</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8457</v>
+        <v>1.0469</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6413</v>
+        <v>-0.5131</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2828</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1991</v>
+        <v>2.3823</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1038</v>
+        <v>0.0317</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1441</v>
+        <v>-0.4928</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2478</v>
+        <v>0.5245</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7602</v>
+        <v>-0.0104</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7602</v>
+        <v>-1.2774</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>H. FABREGAT LORES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.802</v>
+        <v>-1.0884</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3706</v>
+        <v>-2.2213</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4313</v>
+        <v>1.1329</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.3976</v>
+        <v>-0.5006</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6667</v>
+        <v>0.7817</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7309</v>
+        <v>-1.2824</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2695</v>
+        <v>-0.1859</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1799</v>
+        <v>0.4552</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.0896</v>
+        <v>-0.641</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1281</v>
+        <v>-0.3148</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4867</v>
+        <v>0.3265</v>
       </c>
       <c r="O21" t="n">
         <v>-0.6413</v>
       </c>
       <c r="P21" t="n">
-        <v>1.2828</v>
+        <v>-0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5159</v>
+        <v>0.1557</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0565</v>
+        <v>-0.2029</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4594</v>
+        <v>0.3586</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8287</v>
+        <v>-0.0104</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1267</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. FABREGAT LORES</t>
+          <t>J. ROIG MESA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9771</v>
+        <v>-1.5422</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6059</v>
+        <v>-1.5231</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6288</v>
+        <v>-0.0191</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5006</v>
+        <v>-1.8533</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7817</v>
+        <v>-1.9977</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2824</v>
+        <v>0.1444</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1859</v>
+        <v>-0.3663</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4552</v>
+        <v>-1.152</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.641</v>
+        <v>0.7857</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3148</v>
+        <v>-1.487</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3265</v>
+        <v>-0.8457</v>
       </c>
       <c r="O22" t="n">
         <v>-0.6413</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.733</v>
+        <v>1.2828</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0995</v>
+        <v>2.1991</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.733</v>
+        <v>-0.2115</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5875</v>
+        <v>-0.2405</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1456</v>
+        <v>0.029</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.0104</v>
+        <v>-0.7602</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.0104</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. DENIA VIVANCOS</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4513</v>
+        <v>-1.6897</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1104</v>
+        <v>-0.6591</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6591</v>
+        <v>-1.0306</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7365</v>
+        <v>-3.3976</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3067</v>
+        <v>-1.6667</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4298</v>
+        <v>-1.7309</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2703</v>
+        <v>-1.2695</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3536</v>
+        <v>-0.1799</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0833</v>
+        <v>-1.0896</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5338000000000001</v>
+        <v>-2.1281</v>
       </c>
       <c r="N23" t="n">
-        <v>1.0469</v>
+        <v>-1.4867</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5131</v>
+        <v>-0.6413</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3823</v>
+        <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3379</v>
+        <v>-0.4037</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3582</v>
+        <v>-0.345</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0203</v>
+        <v>-0.0586</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.0104</v>
+        <v>0.8287</v>
       </c>
       <c r="W23" t="n">
-        <v>1.267</v>
+        <v>0.9554</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2774</v>
+        <v>-0.1267</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2687</v>
+        <v>-3.8354</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1879</v>
+        <v>-2.9571</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0808</v>
+        <v>-0.8783</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2531</v>
@@ -2326,13 +2326,13 @@
         <v>2.1991</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5247000000000001</v>
+        <v>-0.042</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5468</v>
+        <v>-0.2224</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0221</v>
+        <v>0.1804</v>
       </c>
       <c r="V24" t="n">
         <v>-3.9068</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.7604</v>
+        <v>-5.9124</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.89</v>
+        <v>-5.7938</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-0.1186</v>
       </c>
       <c r="G25" t="n">
         <v>-3.8064</v>
@@ -2404,13 +2404,13 @@
         <v>1.6493</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5875</v>
+        <v>0.2606</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2036</v>
+        <v>-0.1074</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3839</v>
+        <v>0.368</v>
       </c>
       <c r="V25" t="n">
         <v>-1.267</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.2058</v>
+        <v>-11.2828</v>
       </c>
       <c r="E26" t="n">
-        <v>-16.1687</v>
+        <v>-16.1685</v>
       </c>
       <c r="F26" t="n">
-        <v>2.962700000000001</v>
+        <v>4.885800000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-9.821899999999999</v>
@@ -2482,13 +2482,13 @@
         <v>18.3257</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3764</v>
+        <v>0.5468000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.2275</v>
+        <v>-3.2274</v>
       </c>
       <c r="U26" t="n">
-        <v>1.8511</v>
+        <v>3.7743</v>
       </c>
       <c r="V26" t="n">
         <v>-4.756399999999999</v>
@@ -2497,7 +2497,7 @@
         <v>4.486499999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.242799999999999</v>
+        <v>-9.242800000000001</v>
       </c>
     </row>
   </sheetData>
